--- a/tools/importer/reports/import-acesso-informacao-hub.report.xlsx
+++ b/tools/importer/reports/import-acesso-informacao-hub.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="317">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,7 +52,7 @@
     <t>acesso-informacao-hub</t>
   </si>
   <si>
-    <t>2026-07-19T10:24:09.698Z</t>
+    <t>2026-07-19T11:37:34.004Z</t>
   </si>
   <si>
     <t>PBIO | Acesso à Informação</t>
@@ -61,6 +61,39 @@
     <t>https://pbio.com.br/acesso-a-informacao</t>
   </si>
   <si>
+    <t>cartas-de-governanca-e-politicas-publicas.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner"]</t>
+  </si>
+  <si>
+    <t>cartas-de-governanca-e-politicas-publicas</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:42:35.552Z</t>
+  </si>
+  <si>
+    <t>Petrobras Biocombustível | Políticas públicas</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/cartas-de-governanca-e-politicas-publicas</t>
+  </si>
+  <si>
+    <t>demonstrativos-de-quadro-de-pessoal-e-acordos-coletivos.report.json</t>
+  </si>
+  <si>
+    <t>demonstrativos-de-quadro-de-pessoal-e-acordos-coletivos</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:42:40.870Z</t>
+  </si>
+  <si>
+    <t>Petrobras Biocombustível | Departamento Pessoal</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/demonstrativos-de-quadro-de-pessoal-e-acordos-coletivos</t>
+  </si>
+  <si>
     <t>index.report.json</t>
   </si>
   <si>
@@ -80,6 +113,855 @@
   </si>
   <si>
     <t>https://pbio.com.br/</t>
+  </si>
+  <si>
+    <t>institucional.report.json</t>
+  </si>
+  <si>
+    <t>institucional</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:42:47.342Z</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/institucional</t>
+  </si>
+  <si>
+    <t>outras-informacoes.report.json</t>
+  </si>
+  <si>
+    <t>outras-informacoes</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:43:38.214Z</t>
+  </si>
+  <si>
+    <t>Petrobras Biocombustível | outras informações</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/outras-informacoes</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/acoes-e-programas.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/acoes-e-programas</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:38:28.244Z</t>
+  </si>
+  <si>
+    <t>PBIO | Ações e Programas</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/acoes-e-programas</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/auditorias.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/auditorias</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:38:57.040Z</t>
+  </si>
+  <si>
+    <t>PBIO | Auditorias</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/auditorias</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/convenios-e-transferencias.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","cards-content-panel-plain"]</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/convenios-e-transferencias</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:39:26.801Z</t>
+  </si>
+  <si>
+    <t>PBIO | Convênios e Transferências</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/convenios-e-transferencias</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/dados-abertos.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/dados-abertos</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:39:32.633Z</t>
+  </si>
+  <si>
+    <t>PBIO | Dados Abertos</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/dados-abertos</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/empregados-publicos.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/empregados-publicos</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:39:37.517Z</t>
+  </si>
+  <si>
+    <t>PBIO | Empregados Públicos</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/empregados-publicos</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/informacoes-classificadas.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/informacoes-classificadas</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:39:42.776Z</t>
+  </si>
+  <si>
+    <t>PBIO | Informações Classificadas</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/informacoes-classificadas</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/institucional.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/institucional</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:37:40.444Z</t>
+  </si>
+  <si>
+    <t>PBIO | Informações institucionais</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/institucional</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/licitacoes-e-contratos.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/licitacoes-e-contratos</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:39:48.123Z</t>
+  </si>
+  <si>
+    <t>PBIO | Licitações e Contratos</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/licitacoes-e-contratos</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/participacao-social.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/participacao-social</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:40:30.299Z</t>
+  </si>
+  <si>
+    <t>PBIO | Participação Social</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/participacao-social</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/perguntas-frequentes.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/perguntas-frequentes</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:41:07.933Z</t>
+  </si>
+  <si>
+    <t>PBIO | FAQ</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/perguntas-frequentes</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/receitas-e-despesas.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/receitas-e-despesas</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:41:14.846Z</t>
+  </si>
+  <si>
+    <t>PBIO | Receitas e Despesas</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/receitas-e-despesas</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/sancoes-administrativas.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/sancoes-administrativas</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:42:08.809Z</t>
+  </si>
+  <si>
+    <t>PBIO | Sanções Administrativas</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/sancoes-administrativas</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/servico-de-informacao-ao-cidadao-sic.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/servico-de-informacao-ao-cidadao-sic</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:42:13.839Z</t>
+  </si>
+  <si>
+    <t>PBIO | SIC</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/servico-de-informacao-ao-cidadao-sic</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/transparencia-e-prestacao-de-contas.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/transparencia-e-prestacao-de-contas</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:42:30.075Z</t>
+  </si>
+  <si>
+    <t>PBIO | Transparência</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/transparencia-e-prestacao-de-contas</t>
+  </si>
+  <si>
+    <t>institucional/auditoria.report.json</t>
+  </si>
+  <si>
+    <t>institucional/auditoria</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:42:54.037Z</t>
+  </si>
+  <si>
+    <t>Petrobras Biocombustível | Auditoria</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/institucional/auditoria</t>
+  </si>
+  <si>
+    <t>institucional/licitacoes-contratos-e-aquisicao-de-bens.report.json</t>
+  </si>
+  <si>
+    <t>institucional/licitacoes-contratos-e-aquisicao-de-bens</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:42:59.442Z</t>
+  </si>
+  <si>
+    <t>Petrobras Biocombustível | Licitações</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/institucional/licitacoes-contratos-e-aquisicao-de-bens</t>
+  </si>
+  <si>
+    <t>institucional/orgaos-estatutarios.report.json</t>
+  </si>
+  <si>
+    <t>institucional/orgaos-estatutarios</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:43:16.486Z</t>
+  </si>
+  <si>
+    <t>Petrobras Biocombustível | Órgãos</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/institucional/orgaos-estatutarios</t>
+  </si>
+  <si>
+    <t>institucional/relatorios-anuais-e-informacoes-financeiras.report.json</t>
+  </si>
+  <si>
+    <t>institucional/relatorios-anuais-e-informacoes-financeiras</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:43:26.544Z</t>
+  </si>
+  <si>
+    <t>Petrobras Biocombustível | Informações financeiras</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/institucional/relatorios-anuais-e-informacoes-financeiras</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/acoes-e-programas/carta-de-servicos.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","cards-content-panel-plain","cards-content-panel-plain"]</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/acoes-e-programas/carta-de-servicos</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:38:32.926Z</t>
+  </si>
+  <si>
+    <t>PBIO | Carta de Serviços</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/acoes-e-programas/carta-de-servicos</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/acoes-e-programas/governanca.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/acoes-e-programas/governanca</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:38:39.033Z</t>
+  </si>
+  <si>
+    <t>PBIO | Governança</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/acoes-e-programas/governanca</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/acoes-e-programas/programas-finalisticos.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/acoes-e-programas/programas-finalisticos</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:38:44.911Z</t>
+  </si>
+  <si>
+    <t>PBIO | Programas Finalísticos</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/acoes-e-programas/programas-finalisticos</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/acoes-e-programas/recursos-financeiros-renuncia-de-receitas.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/acoes-e-programas/recursos-financeiros-renuncia-de-receitas</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:38:51.084Z</t>
+  </si>
+  <si>
+    <t>PBIO | Concessões de Recursos e Renúncias de Receitas</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/acoes-e-programas/recursos-financeiros-renuncia-de-receitas</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/auditorias/acoes-de-supervisao-controle-e-correicao.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/auditorias/acoes-de-supervisao-controle-e-correicao</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:39:03.154Z</t>
+  </si>
+  <si>
+    <t>PBIO | Supervisão, Controle e correição</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/auditorias/acoes-de-supervisao-controle-e-correicao</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/auditorias/demonstracoes-financeiras.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/auditorias/demonstracoes-financeiras</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:39:08.744Z</t>
+  </si>
+  <si>
+    <t>PBIO | Demonstrações Financeiras</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/auditorias/demonstracoes-financeiras</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/auditorias/prestacao-de-contas.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/auditorias/prestacao-de-contas</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:39:15.224Z</t>
+  </si>
+  <si>
+    <t>PBIO | Prestação de Contas</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/auditorias/prestacao-de-contas</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/auditorias/relatorios-da-cgu.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/auditorias/relatorios-da-cgu</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:39:19.618Z</t>
+  </si>
+  <si>
+    <t>PBIO | Relatórios da CGU</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/auditorias/relatorios-da-cgu</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/institucional/agenda-de-autoridades.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","embed"]</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/institucional/agenda-de-autoridades</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:52:54.539Z</t>
+  </si>
+  <si>
+    <t>PBIO | Agenda de Autoridades</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/institucional/agenda-de-autoridades</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/institucional/atas.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/institucional/atas</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:38:01.888Z</t>
+  </si>
+  <si>
+    <t>PBIO | Atas</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/institucional/atas</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/institucional/atos-normativos.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/institucional/atos-normativos</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:38:07.463Z</t>
+  </si>
+  <si>
+    <t>PBIO | Atos normativos</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/institucional/atos-normativos</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/institucional/horario-de-atendimento.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/institucional/horario-de-atendimento</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:38:11.770Z</t>
+  </si>
+  <si>
+    <t>PBIO | Horário de Atendimento</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/institucional/horario-de-atendimento</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/institucional/hospitalidades.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/institucional/hospitalidades</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:38:16.176Z</t>
+  </si>
+  <si>
+    <t>PBIO | Hospitalidades Recebidas</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/institucional/hospitalidades</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/institucional/presentes.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/institucional/presentes</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:38:23.020Z</t>
+  </si>
+  <si>
+    <t>PBIO | Presentes Recebidos</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/institucional/presentes</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/institucional/sobre.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/institucional/sobre</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:37:47.432Z</t>
+  </si>
+  <si>
+    <t>PBIO | Quem Somos</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/institucional/sobre</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/licitacoes-e-contratos/aditivos.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/licitacoes-e-contratos/aditivos</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:39:54.935Z</t>
+  </si>
+  <si>
+    <t>PBIO | Aditivos</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/licitacoes-e-contratos/aditivos</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/licitacoes-e-contratos/contratos-de-transferencia-de-tecnologia.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/licitacoes-e-contratos/contratos-de-transferencia-de-tecnologia</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:40:09.000Z</t>
+  </si>
+  <si>
+    <t>PBIO | Contratos de Transferência de Tecnologia</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/licitacoes-e-contratos/contratos-de-transferencia-de-tecnologia</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/licitacoes-e-contratos/contratos.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/licitacoes-e-contratos/contratos</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:40:02.294Z</t>
+  </si>
+  <si>
+    <t>PBIO | Contratos</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/licitacoes-e-contratos/contratos</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/licitacoes-e-contratos/licitacoes.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/licitacoes-e-contratos/licitacoes</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:40:17.478Z</t>
+  </si>
+  <si>
+    <t>PBIO | Licitações</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/licitacoes-e-contratos/licitacoes</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/licitacoes-e-contratos/patrocinios.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/licitacoes-e-contratos/patrocinios</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:40:22.984Z</t>
+  </si>
+  <si>
+    <t>PBIO | Patrocínios</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/licitacoes-e-contratos/patrocinios</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/participacao-social/audiencias-publicas.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/participacao-social/audiencias-publicas</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:40:35.859Z</t>
+  </si>
+  <si>
+    <t>PBIO | Audiências Públicas</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/participacao-social/audiencias-publicas</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/participacao-social/conferencias.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/participacao-social/conferencias</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:40:40.486Z</t>
+  </si>
+  <si>
+    <t>PBIO | Conferências</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/participacao-social/conferencias</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/participacao-social/conselhos-e-orgaos-colegiados.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/participacao-social/conselhos-e-orgaos-colegiados</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:40:45.720Z</t>
+  </si>
+  <si>
+    <t>PBIO | Conselhos e Órgãos Colegiados</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/participacao-social/conselhos-e-orgaos-colegiados</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/participacao-social/editais-de-chamamento-publico.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/participacao-social/editais-de-chamamento-publico</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:40:50.831Z</t>
+  </si>
+  <si>
+    <t>PBIO | Editais de Chamamento Público</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/participacao-social/editais-de-chamamento-publico</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/participacao-social/outras-acoes.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/participacao-social/outras-acoes</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:40:55.397Z</t>
+  </si>
+  <si>
+    <t>PBIO | Outras Ações</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/participacao-social/outras-acoes</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/participacao-social/ouvidoria.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/participacao-social/ouvidoria</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:41:01.714Z</t>
+  </si>
+  <si>
+    <t>PBIO | Ouvidoria</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/participacao-social/ouvidoria</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/receitas-e-despesas/alienacao-de-bens-imoveis.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/receitas-e-despesas/alienacao-de-bens-imoveis</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:41:20.846Z</t>
+  </si>
+  <si>
+    <t>PBIO | Alienação de Bens Imóveis</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/receitas-e-despesas/alienacao-de-bens-imoveis</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/receitas-e-despesas/aquisicao-de-bens.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/receitas-e-despesas/aquisicao-de-bens</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:41:27.311Z</t>
+  </si>
+  <si>
+    <t>PBIO | Aquisição de Bens</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/receitas-e-despesas/aquisicao-de-bens</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/receitas-e-despesas/diarias-e-passagens.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/receitas-e-despesas/diarias-e-passagens</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:41:32.931Z</t>
+  </si>
+  <si>
+    <t>PBIO | Diárias e Passagens</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/receitas-e-despesas/diarias-e-passagens</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/receitas-e-despesas/orcamento-de-investimento.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","table","table"]</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/receitas-e-despesas/orcamento-de-investimento</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:41:39.094Z</t>
+  </si>
+  <si>
+    <t>PBIO | Orçamento de Investimento</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/receitas-e-despesas/orcamento-de-investimento</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/receitas-e-despesas/politica-de-dividendos.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/receitas-e-despesas/politica-de-dividendos</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:41:45.080Z</t>
+  </si>
+  <si>
+    <t>PBIO | Política de Dividendos</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/receitas-e-despesas/politica-de-dividendos</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/receitas-e-despesas/politica-de-transacoes-com-partes-relacionadas.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/receitas-e-despesas/politica-de-transacoes-com-partes-relacionadas</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:41:50.583Z</t>
+  </si>
+  <si>
+    <t>PBIO | Política de Transações</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/receitas-e-despesas/politica-de-transacoes-com-partes-relacionadas</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/receitas-e-despesas/publicidade.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/receitas-e-despesas/publicidade</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:41:56.011Z</t>
+  </si>
+  <si>
+    <t>PBIO | Publicidade</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/receitas-e-despesas/publicidade</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/receitas-e-despesas/receitas.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/receitas-e-despesas/receitas</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:42:01.484Z</t>
+  </si>
+  <si>
+    <t>PBIO | Receitas</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/receitas-e-despesas/receitas</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/servico-de-informacao-ao-cidadao-sic/balcoes-de-atendimento.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/servico-de-informacao-ao-cidadao-sic/balcoes-de-atendimento</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:42:20.110Z</t>
+  </si>
+  <si>
+    <t>PBIO | Atendimento</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/servico-de-informacao-ao-cidadao-sic/balcoes-de-atendimento</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/servico-de-informacao-ao-cidadao-sic/estatisticas-do-sic.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/servico-de-informacao-ao-cidadao-sic/estatisticas-do-sic</t>
+  </si>
+  <si>
+    <t>2026-07-19T11:42:24.836Z</t>
+  </si>
+  <si>
+    <t>PBIO | Estatísticas do SIC</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/servico-de-informacao-ao-cidadao-sic/estatisticas-do-sic</t>
   </si>
 </sst>
 </file>
@@ -468,16 +1350,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="33" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="1" max="3" width="50" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="41" customWidth="1"/>
+    <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -546,16 +1425,1524 @@
         <v>11</v>
       </c>
       <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>21</v>
       </c>
-      <c r="H3" t="s">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" t="s">
+        <v>62</v>
+      </c>
+      <c r="H11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" t="s">
+        <v>67</v>
+      </c>
+      <c r="H12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" t="s">
+        <v>82</v>
+      </c>
+      <c r="H15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
+        <v>86</v>
+      </c>
+      <c r="G16" t="s">
+        <v>87</v>
+      </c>
+      <c r="H16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" t="s">
+        <v>91</v>
+      </c>
+      <c r="G17" t="s">
+        <v>92</v>
+      </c>
+      <c r="H17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" t="s">
+        <v>96</v>
+      </c>
+      <c r="G18" t="s">
+        <v>97</v>
+      </c>
+      <c r="H18" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>99</v>
+      </c>
+      <c r="B19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" t="s">
+        <v>101</v>
+      </c>
+      <c r="G19" t="s">
+        <v>102</v>
+      </c>
+      <c r="H19" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" t="s">
+        <v>106</v>
+      </c>
+      <c r="G20" t="s">
+        <v>107</v>
+      </c>
+      <c r="H20" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>109</v>
+      </c>
+      <c r="B21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" t="s">
+        <v>110</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" t="s">
+        <v>111</v>
+      </c>
+      <c r="G21" t="s">
+        <v>112</v>
+      </c>
+      <c r="H21" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" t="s">
+        <v>115</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" t="s">
+        <v>116</v>
+      </c>
+      <c r="G22" t="s">
+        <v>117</v>
+      </c>
+      <c r="H22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>119</v>
+      </c>
+      <c r="B23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" t="s">
+        <v>120</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" t="s">
+        <v>121</v>
+      </c>
+      <c r="G23" t="s">
+        <v>122</v>
+      </c>
+      <c r="H23" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>124</v>
+      </c>
+      <c r="B24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" t="s">
+        <v>125</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" t="s">
+        <v>126</v>
+      </c>
+      <c r="G24" t="s">
+        <v>127</v>
+      </c>
+      <c r="H24" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>129</v>
+      </c>
+      <c r="B25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" t="s">
+        <v>130</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" t="s">
+        <v>131</v>
+      </c>
+      <c r="G25" t="s">
+        <v>132</v>
+      </c>
+      <c r="H25" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>134</v>
+      </c>
+      <c r="B26" t="s">
+        <v>135</v>
+      </c>
+      <c r="C26" t="s">
+        <v>136</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" t="s">
+        <v>137</v>
+      </c>
+      <c r="G26" t="s">
+        <v>138</v>
+      </c>
+      <c r="H26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>140</v>
+      </c>
+      <c r="B27" t="s">
+        <v>135</v>
+      </c>
+      <c r="C27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" t="s">
+        <v>142</v>
+      </c>
+      <c r="G27" t="s">
+        <v>143</v>
+      </c>
+      <c r="H27" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>145</v>
+      </c>
+      <c r="B28" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" t="s">
+        <v>146</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" t="s">
+        <v>147</v>
+      </c>
+      <c r="G28" t="s">
+        <v>148</v>
+      </c>
+      <c r="H28" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>150</v>
+      </c>
+      <c r="B29" t="s">
+        <v>135</v>
+      </c>
+      <c r="C29" t="s">
+        <v>151</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" t="s">
+        <v>152</v>
+      </c>
+      <c r="G29" t="s">
+        <v>153</v>
+      </c>
+      <c r="H29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>155</v>
+      </c>
+      <c r="B30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" t="s">
+        <v>156</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" t="s">
+        <v>157</v>
+      </c>
+      <c r="G30" t="s">
+        <v>158</v>
+      </c>
+      <c r="H30" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>160</v>
+      </c>
+      <c r="B31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" t="s">
+        <v>161</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" t="s">
+        <v>162</v>
+      </c>
+      <c r="G31" t="s">
+        <v>163</v>
+      </c>
+      <c r="H31" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>165</v>
+      </c>
+      <c r="B32" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" t="s">
+        <v>166</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" t="s">
+        <v>167</v>
+      </c>
+      <c r="G32" t="s">
+        <v>168</v>
+      </c>
+      <c r="H32" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>170</v>
+      </c>
+      <c r="B33" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" t="s">
+        <v>171</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" t="s">
+        <v>172</v>
+      </c>
+      <c r="G33" t="s">
+        <v>173</v>
+      </c>
+      <c r="H33" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>175</v>
+      </c>
+      <c r="B34" t="s">
+        <v>176</v>
+      </c>
+      <c r="C34" t="s">
+        <v>177</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" t="s">
+        <v>178</v>
+      </c>
+      <c r="G34" t="s">
+        <v>179</v>
+      </c>
+      <c r="H34" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>181</v>
+      </c>
+      <c r="B35" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" t="s">
+        <v>182</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" t="s">
+        <v>183</v>
+      </c>
+      <c r="G35" t="s">
+        <v>184</v>
+      </c>
+      <c r="H35" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>186</v>
+      </c>
+      <c r="B36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" t="s">
+        <v>187</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" t="s">
+        <v>188</v>
+      </c>
+      <c r="G36" t="s">
+        <v>189</v>
+      </c>
+      <c r="H36" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>191</v>
+      </c>
+      <c r="B37" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" t="s">
+        <v>192</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" t="s">
+        <v>193</v>
+      </c>
+      <c r="G37" t="s">
+        <v>194</v>
+      </c>
+      <c r="H37" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>196</v>
+      </c>
+      <c r="B38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" t="s">
+        <v>197</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" t="s">
+        <v>198</v>
+      </c>
+      <c r="G38" t="s">
+        <v>199</v>
+      </c>
+      <c r="H38" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>201</v>
+      </c>
+      <c r="B39" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" t="s">
+        <v>202</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" t="s">
+        <v>203</v>
+      </c>
+      <c r="G39" t="s">
+        <v>204</v>
+      </c>
+      <c r="H39" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>206</v>
+      </c>
+      <c r="B40" t="s">
+        <v>17</v>
+      </c>
+      <c r="C40" t="s">
+        <v>207</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" t="s">
+        <v>208</v>
+      </c>
+      <c r="G40" t="s">
+        <v>209</v>
+      </c>
+      <c r="H40" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>211</v>
+      </c>
+      <c r="B41" t="s">
+        <v>17</v>
+      </c>
+      <c r="C41" t="s">
+        <v>212</v>
+      </c>
+      <c r="D41" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" t="s">
+        <v>213</v>
+      </c>
+      <c r="G41" t="s">
+        <v>214</v>
+      </c>
+      <c r="H41" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>216</v>
+      </c>
+      <c r="B42" t="s">
+        <v>54</v>
+      </c>
+      <c r="C42" t="s">
+        <v>217</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" t="s">
+        <v>218</v>
+      </c>
+      <c r="G42" t="s">
+        <v>219</v>
+      </c>
+      <c r="H42" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>221</v>
+      </c>
+      <c r="B43" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" t="s">
+        <v>222</v>
+      </c>
+      <c r="D43" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43" t="s">
+        <v>223</v>
+      </c>
+      <c r="G43" t="s">
+        <v>224</v>
+      </c>
+      <c r="H43" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>226</v>
+      </c>
+      <c r="B44" t="s">
+        <v>54</v>
+      </c>
+      <c r="C44" t="s">
+        <v>227</v>
+      </c>
+      <c r="D44" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" t="s">
+        <v>228</v>
+      </c>
+      <c r="G44" t="s">
+        <v>229</v>
+      </c>
+      <c r="H44" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>231</v>
+      </c>
+      <c r="B45" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" t="s">
+        <v>232</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" t="s">
+        <v>233</v>
+      </c>
+      <c r="G45" t="s">
+        <v>234</v>
+      </c>
+      <c r="H45" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>236</v>
+      </c>
+      <c r="B46" t="s">
+        <v>54</v>
+      </c>
+      <c r="C46" t="s">
+        <v>237</v>
+      </c>
+      <c r="D46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" t="s">
+        <v>238</v>
+      </c>
+      <c r="G46" t="s">
+        <v>239</v>
+      </c>
+      <c r="H46" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>241</v>
+      </c>
+      <c r="B47" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" t="s">
+        <v>242</v>
+      </c>
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" t="s">
+        <v>243</v>
+      </c>
+      <c r="G47" t="s">
+        <v>244</v>
+      </c>
+      <c r="H47" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>246</v>
+      </c>
+      <c r="B48" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" t="s">
+        <v>247</v>
+      </c>
+      <c r="D48" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" t="s">
+        <v>248</v>
+      </c>
+      <c r="G48" t="s">
+        <v>249</v>
+      </c>
+      <c r="H48" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>251</v>
+      </c>
+      <c r="B49" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" t="s">
+        <v>252</v>
+      </c>
+      <c r="D49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" t="s">
+        <v>12</v>
+      </c>
+      <c r="F49" t="s">
+        <v>253</v>
+      </c>
+      <c r="G49" t="s">
+        <v>254</v>
+      </c>
+      <c r="H49" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>256</v>
+      </c>
+      <c r="B50" t="s">
+        <v>54</v>
+      </c>
+      <c r="C50" t="s">
+        <v>257</v>
+      </c>
+      <c r="D50" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" t="s">
+        <v>258</v>
+      </c>
+      <c r="G50" t="s">
+        <v>259</v>
+      </c>
+      <c r="H50" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>261</v>
+      </c>
+      <c r="B51" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" t="s">
+        <v>262</v>
+      </c>
+      <c r="D51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" t="s">
+        <v>263</v>
+      </c>
+      <c r="G51" t="s">
+        <v>264</v>
+      </c>
+      <c r="H51" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>266</v>
+      </c>
+      <c r="B52" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" t="s">
+        <v>267</v>
+      </c>
+      <c r="D52" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" t="s">
+        <v>268</v>
+      </c>
+      <c r="G52" t="s">
+        <v>269</v>
+      </c>
+      <c r="H52" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>271</v>
+      </c>
+      <c r="B53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" t="s">
+        <v>272</v>
+      </c>
+      <c r="D53" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" t="s">
+        <v>12</v>
+      </c>
+      <c r="F53" t="s">
+        <v>273</v>
+      </c>
+      <c r="G53" t="s">
+        <v>274</v>
+      </c>
+      <c r="H53" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>276</v>
+      </c>
+      <c r="B54" t="s">
+        <v>54</v>
+      </c>
+      <c r="C54" t="s">
+        <v>277</v>
+      </c>
+      <c r="D54" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" t="s">
+        <v>278</v>
+      </c>
+      <c r="G54" t="s">
+        <v>279</v>
+      </c>
+      <c r="H54" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>281</v>
+      </c>
+      <c r="B55" t="s">
+        <v>282</v>
+      </c>
+      <c r="C55" t="s">
+        <v>283</v>
+      </c>
+      <c r="D55" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55" t="s">
+        <v>284</v>
+      </c>
+      <c r="G55" t="s">
+        <v>285</v>
+      </c>
+      <c r="H55" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>287</v>
+      </c>
+      <c r="B56" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56" t="s">
+        <v>288</v>
+      </c>
+      <c r="D56" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" t="s">
+        <v>289</v>
+      </c>
+      <c r="G56" t="s">
+        <v>290</v>
+      </c>
+      <c r="H56" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>292</v>
+      </c>
+      <c r="B57" t="s">
+        <v>17</v>
+      </c>
+      <c r="C57" t="s">
+        <v>293</v>
+      </c>
+      <c r="D57" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" t="s">
+        <v>12</v>
+      </c>
+      <c r="F57" t="s">
+        <v>294</v>
+      </c>
+      <c r="G57" t="s">
+        <v>295</v>
+      </c>
+      <c r="H57" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>297</v>
+      </c>
+      <c r="B58" t="s">
+        <v>54</v>
+      </c>
+      <c r="C58" t="s">
+        <v>298</v>
+      </c>
+      <c r="D58" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" t="s">
+        <v>299</v>
+      </c>
+      <c r="G58" t="s">
+        <v>300</v>
+      </c>
+      <c r="H58" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>302</v>
+      </c>
+      <c r="B59" t="s">
+        <v>17</v>
+      </c>
+      <c r="C59" t="s">
+        <v>303</v>
+      </c>
+      <c r="D59" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59" t="s">
+        <v>12</v>
+      </c>
+      <c r="F59" t="s">
+        <v>304</v>
+      </c>
+      <c r="G59" t="s">
+        <v>305</v>
+      </c>
+      <c r="H59" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>307</v>
+      </c>
+      <c r="B60" t="s">
+        <v>17</v>
+      </c>
+      <c r="C60" t="s">
+        <v>308</v>
+      </c>
+      <c r="D60" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" t="s">
+        <v>309</v>
+      </c>
+      <c r="G60" t="s">
+        <v>310</v>
+      </c>
+      <c r="H60" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>312</v>
+      </c>
+      <c r="B61" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" t="s">
+        <v>313</v>
+      </c>
+      <c r="D61" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" t="s">
+        <v>12</v>
+      </c>
+      <c r="F61" t="s">
+        <v>314</v>
+      </c>
+      <c r="G61" t="s">
+        <v>315</v>
+      </c>
+      <c r="H61" t="s">
+        <v>316</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-acesso-informacao-hub.report.xlsx
+++ b/tools/importer/reports/import-acesso-informacao-hub.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="326">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,7 +52,7 @@
     <t>acesso-informacao-hub</t>
   </si>
   <si>
-    <t>2026-07-19T11:37:34.004Z</t>
+    <t>2026-07-19T18:51:41.740Z</t>
   </si>
   <si>
     <t>PBIO | Acesso à Informação</t>
@@ -64,91 +64,106 @@
     <t>cartas-de-governanca-e-politicas-publicas.report.json</t>
   </si>
   <si>
+    <t>["hero-banner","anchornav-sticky","downloads-accordion","downloads-accordion"]</t>
+  </si>
+  <si>
+    <t>cartas-de-governanca-e-politicas-publicas</t>
+  </si>
+  <si>
+    <t>institucional-anchor</t>
+  </si>
+  <si>
+    <t>2026-07-19T18:51:18.970Z</t>
+  </si>
+  <si>
+    <t>Petrobras Biocombustível | Políticas públicas</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/cartas-de-governanca-e-politicas-publicas</t>
+  </si>
+  <si>
+    <t>demonstrativos-de-quadro-de-pessoal-e-acordos-coletivos.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","anchornav-sticky","downloads-accordion"]</t>
+  </si>
+  <si>
+    <t>demonstrativos-de-quadro-de-pessoal-e-acordos-coletivos</t>
+  </si>
+  <si>
+    <t>2026-07-19T18:51:23.588Z</t>
+  </si>
+  <si>
+    <t>Petrobras Biocombustível | Departamento Pessoal</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/demonstrativos-de-quadro-de-pessoal-e-acordos-coletivos</t>
+  </si>
+  <si>
+    <t>index.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","anchornav-sticky","cards-content-panel","cards-content-panel","cards-content-panel","cards-content-panel","cards-content-panel","cards-content-panel"]</t>
+  </si>
+  <si>
+    <t>index</t>
+  </si>
+  <si>
+    <t>institucional-page</t>
+  </si>
+  <si>
+    <t>2026-07-18T12:06:39.909Z</t>
+  </si>
+  <si>
+    <t>Petrobras Biocombustível</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/</t>
+  </si>
+  <si>
+    <t>institucional.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","anchornav-sticky"]</t>
+  </si>
+  <si>
+    <t>institucional</t>
+  </si>
+  <si>
+    <t>2026-07-19T18:50:31.700Z</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/institucional</t>
+  </si>
+  <si>
+    <t>outras-informacoes.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","anchornav-sticky","downloads-accordion","downloads-accordion","downloads-accordion","downloads-accordion","downloads-accordion","downloads-accordion","downloads-accordion","downloads-accordion"]</t>
+  </si>
+  <si>
+    <t>outras-informacoes</t>
+  </si>
+  <si>
+    <t>2026-07-19T18:51:34.502Z</t>
+  </si>
+  <si>
+    <t>Petrobras Biocombustível | outras informações</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/outras-informacoes</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/acoes-e-programas.report.json</t>
+  </si>
+  <si>
     <t>["hero-banner"]</t>
   </si>
   <si>
-    <t>cartas-de-governanca-e-politicas-publicas</t>
-  </si>
-  <si>
-    <t>2026-07-19T11:42:35.552Z</t>
-  </si>
-  <si>
-    <t>Petrobras Biocombustível | Políticas públicas</t>
-  </si>
-  <si>
-    <t>https://pbio.com.br/cartas-de-governanca-e-politicas-publicas</t>
-  </si>
-  <si>
-    <t>demonstrativos-de-quadro-de-pessoal-e-acordos-coletivos.report.json</t>
-  </si>
-  <si>
-    <t>demonstrativos-de-quadro-de-pessoal-e-acordos-coletivos</t>
-  </si>
-  <si>
-    <t>2026-07-19T11:42:40.870Z</t>
-  </si>
-  <si>
-    <t>Petrobras Biocombustível | Departamento Pessoal</t>
-  </si>
-  <si>
-    <t>https://pbio.com.br/demonstrativos-de-quadro-de-pessoal-e-acordos-coletivos</t>
-  </si>
-  <si>
-    <t>index.report.json</t>
-  </si>
-  <si>
-    <t>["hero-banner","anchornav-sticky","cards-content-panel","cards-content-panel","cards-content-panel","cards-content-panel","cards-content-panel","cards-content-panel"]</t>
-  </si>
-  <si>
-    <t>index</t>
-  </si>
-  <si>
-    <t>institucional-page</t>
-  </si>
-  <si>
-    <t>2026-07-18T12:06:39.909Z</t>
-  </si>
-  <si>
-    <t>Petrobras Biocombustível</t>
-  </si>
-  <si>
-    <t>https://pbio.com.br/</t>
-  </si>
-  <si>
-    <t>institucional.report.json</t>
-  </si>
-  <si>
-    <t>institucional</t>
-  </si>
-  <si>
-    <t>2026-07-19T11:42:47.342Z</t>
-  </si>
-  <si>
-    <t>https://pbio.com.br/institucional</t>
-  </si>
-  <si>
-    <t>outras-informacoes.report.json</t>
-  </si>
-  <si>
-    <t>outras-informacoes</t>
-  </si>
-  <si>
-    <t>2026-07-19T11:43:38.214Z</t>
-  </si>
-  <si>
-    <t>Petrobras Biocombustível | outras informações</t>
-  </si>
-  <si>
-    <t>https://pbio.com.br/outras-informacoes</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/acoes-e-programas.report.json</t>
-  </si>
-  <si>
     <t>acesso-a-informacao/acoes-e-programas</t>
   </si>
   <si>
-    <t>2026-07-19T11:38:28.244Z</t>
+    <t>2026-07-19T18:52:36.196Z</t>
   </si>
   <si>
     <t>PBIO | Ações e Programas</t>
@@ -163,7 +178,7 @@
     <t>acesso-a-informacao/auditorias</t>
   </si>
   <si>
-    <t>2026-07-19T11:38:57.040Z</t>
+    <t>2026-07-19T18:53:04.101Z</t>
   </si>
   <si>
     <t>PBIO | Auditorias</t>
@@ -175,118 +190,121 @@
     <t>acesso-a-informacao/convenios-e-transferencias.report.json</t>
   </si>
   <si>
+    <t>["hero-banner","cards-content-panel-plain","embed"]</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/convenios-e-transferencias</t>
+  </si>
+  <si>
+    <t>2026-07-19T18:53:35.297Z</t>
+  </si>
+  <si>
+    <t>PBIO | Convênios e Transferências</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/convenios-e-transferencias</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/dados-abertos.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/dados-abertos</t>
+  </si>
+  <si>
+    <t>2026-07-19T18:53:41.861Z</t>
+  </si>
+  <si>
+    <t>PBIO | Dados Abertos</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/dados-abertos</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/empregados-publicos.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/empregados-publicos</t>
+  </si>
+  <si>
+    <t>2026-07-19T18:53:46.846Z</t>
+  </si>
+  <si>
+    <t>PBIO | Empregados Públicos</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/empregados-publicos</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/informacoes-classificadas.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/informacoes-classificadas</t>
+  </si>
+  <si>
+    <t>2026-07-19T18:53:53.220Z</t>
+  </si>
+  <si>
+    <t>PBIO | Informações Classificadas</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/informacoes-classificadas</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/institucional.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/institucional</t>
+  </si>
+  <si>
+    <t>2026-07-19T18:51:47.665Z</t>
+  </si>
+  <si>
+    <t>PBIO | Informações institucionais</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/institucional</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/licitacoes-e-contratos.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/licitacoes-e-contratos</t>
+  </si>
+  <si>
+    <t>2026-07-19T18:53:59.148Z</t>
+  </si>
+  <si>
+    <t>PBIO | Licitações e Contratos</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/licitacoes-e-contratos</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/participacao-social.report.json</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/participacao-social</t>
+  </si>
+  <si>
+    <t>2026-07-19T18:54:38.300Z</t>
+  </si>
+  <si>
+    <t>PBIO | Participação Social</t>
+  </si>
+  <si>
+    <t>https://pbio.com.br/acesso-a-informacao/participacao-social</t>
+  </si>
+  <si>
+    <t>acesso-a-informacao/perguntas-frequentes.report.json</t>
+  </si>
+  <si>
     <t>["hero-banner","cards-content-panel-plain"]</t>
   </si>
   <si>
-    <t>acesso-a-informacao/convenios-e-transferencias</t>
-  </si>
-  <si>
-    <t>2026-07-19T11:39:26.801Z</t>
-  </si>
-  <si>
-    <t>PBIO | Convênios e Transferências</t>
-  </si>
-  <si>
-    <t>https://pbio.com.br/acesso-a-informacao/convenios-e-transferencias</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/dados-abertos.report.json</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/dados-abertos</t>
-  </si>
-  <si>
-    <t>2026-07-19T11:39:32.633Z</t>
-  </si>
-  <si>
-    <t>PBIO | Dados Abertos</t>
-  </si>
-  <si>
-    <t>https://pbio.com.br/acesso-a-informacao/dados-abertos</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/empregados-publicos.report.json</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/empregados-publicos</t>
-  </si>
-  <si>
-    <t>2026-07-19T11:39:37.517Z</t>
-  </si>
-  <si>
-    <t>PBIO | Empregados Públicos</t>
-  </si>
-  <si>
-    <t>https://pbio.com.br/acesso-a-informacao/empregados-publicos</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/informacoes-classificadas.report.json</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/informacoes-classificadas</t>
-  </si>
-  <si>
-    <t>2026-07-19T11:39:42.776Z</t>
-  </si>
-  <si>
-    <t>PBIO | Informações Classificadas</t>
-  </si>
-  <si>
-    <t>https://pbio.com.br/acesso-a-informacao/informacoes-classificadas</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/institucional.report.json</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/institucional</t>
-  </si>
-  <si>
-    <t>2026-07-19T11:37:40.444Z</t>
-  </si>
-  <si>
-    <t>PBIO | Informações institucionais</t>
-  </si>
-  <si>
-    <t>https://pbio.com.br/acesso-a-informacao/institucional</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/licitacoes-e-contratos.report.json</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/licitacoes-e-contratos</t>
-  </si>
-  <si>
-    <t>2026-07-19T11:39:48.123Z</t>
-  </si>
-  <si>
-    <t>PBIO | Licitações e Contratos</t>
-  </si>
-  <si>
-    <t>https://pbio.com.br/acesso-a-informacao/licitacoes-e-contratos</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/participacao-social.report.json</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/participacao-social</t>
-  </si>
-  <si>
-    <t>2026-07-19T11:40:30.299Z</t>
-  </si>
-  <si>
-    <t>PBIO | Participação Social</t>
-  </si>
-  <si>
-    <t>https://pbio.com.br/acesso-a-informacao/participacao-social</t>
-  </si>
-  <si>
-    <t>acesso-a-informacao/perguntas-frequentes.report.json</t>
-  </si>
-  <si>
     <t>acesso-a-informacao/perguntas-frequentes</t>
   </si>
   <si>
-    <t>2026-07-19T11:41:07.933Z</t>
+    <t>2026-07-19T19:04:51.652Z</t>
   </si>
   <si>
     <t>PBIO | FAQ</t>
@@ -301,7 +319,7 @@
     <t>acesso-a-informacao/receitas-e-despesas</t>
   </si>
   <si>
-    <t>2026-07-19T11:41:14.846Z</t>
+    <t>2026-07-19T19:04:57.667Z</t>
   </si>
   <si>
     <t>PBIO | Receitas e Despesas</t>
@@ -316,7 +334,7 @@
     <t>acesso-a-informacao/sancoes-administrativas</t>
   </si>
   <si>
-    <t>2026-07-19T11:42:08.809Z</t>
+    <t>2026-07-19T19:05:51.598Z</t>
   </si>
   <si>
     <t>PBIO | Sanções Administrativas</t>
@@ -331,7 +349,7 @@
     <t>acesso-a-informacao/servico-de-informacao-ao-cidadao-sic</t>
   </si>
   <si>
-    <t>2026-07-19T11:42:13.839Z</t>
+    <t>2026-07-19T19:05:56.728Z</t>
   </si>
   <si>
     <t>PBIO | SIC</t>
@@ -346,7 +364,7 @@
     <t>acesso-a-informacao/transparencia-e-prestacao-de-contas</t>
   </si>
   <si>
-    <t>2026-07-19T11:42:30.075Z</t>
+    <t>2026-07-19T19:06:13.327Z</t>
   </si>
   <si>
     <t>PBIO | Transparência</t>
@@ -361,7 +379,7 @@
     <t>institucional/auditoria</t>
   </si>
   <si>
-    <t>2026-07-19T11:42:54.037Z</t>
+    <t>2026-07-19T18:50:38.808Z</t>
   </si>
   <si>
     <t>Petrobras Biocombustível | Auditoria</t>
@@ -376,7 +394,7 @@
     <t>institucional/licitacoes-contratos-e-aquisicao-de-bens</t>
   </si>
   <si>
-    <t>2026-07-19T11:42:59.442Z</t>
+    <t>2026-07-19T18:50:43.843Z</t>
   </si>
   <si>
     <t>Petrobras Biocombustível | Licitações</t>
@@ -388,10 +406,13 @@
     <t>institucional/orgaos-estatutarios.report.json</t>
   </si>
   <si>
+    <t>["hero-banner","anchornav-sticky","downloads-accordion","downloads-accordion","accordion-nested","downloads-accordion"]</t>
+  </si>
+  <si>
     <t>institucional/orgaos-estatutarios</t>
   </si>
   <si>
-    <t>2026-07-19T11:43:16.486Z</t>
+    <t>2026-07-19T18:51:01.368Z</t>
   </si>
   <si>
     <t>Petrobras Biocombustível | Órgãos</t>
@@ -403,10 +424,13 @@
     <t>institucional/relatorios-anuais-e-informacoes-financeiras.report.json</t>
   </si>
   <si>
+    <t>["hero-banner","anchornav-sticky","downloads-accordion","downloads-accordion","downloads-accordion","downloads-accordion","downloads-accordion"]</t>
+  </si>
+  <si>
     <t>institucional/relatorios-anuais-e-informacoes-financeiras</t>
   </si>
   <si>
-    <t>2026-07-19T11:43:26.544Z</t>
+    <t>2026-07-19T18:51:10.498Z</t>
   </si>
   <si>
     <t>Petrobras Biocombustível | Informações financeiras</t>
@@ -424,7 +448,7 @@
     <t>acesso-a-informacao/acoes-e-programas/carta-de-servicos</t>
   </si>
   <si>
-    <t>2026-07-19T11:38:32.926Z</t>
+    <t>2026-07-19T18:52:42.101Z</t>
   </si>
   <si>
     <t>PBIO | Carta de Serviços</t>
@@ -439,7 +463,7 @@
     <t>acesso-a-informacao/acoes-e-programas/governanca</t>
   </si>
   <si>
-    <t>2026-07-19T11:38:39.033Z</t>
+    <t>2026-07-19T18:52:48.035Z</t>
   </si>
   <si>
     <t>PBIO | Governança</t>
@@ -454,7 +478,7 @@
     <t>acesso-a-informacao/acoes-e-programas/programas-finalisticos</t>
   </si>
   <si>
-    <t>2026-07-19T11:38:44.911Z</t>
+    <t>2026-07-19T18:52:53.679Z</t>
   </si>
   <si>
     <t>PBIO | Programas Finalísticos</t>
@@ -469,7 +493,7 @@
     <t>acesso-a-informacao/acoes-e-programas/recursos-financeiros-renuncia-de-receitas</t>
   </si>
   <si>
-    <t>2026-07-19T11:38:51.084Z</t>
+    <t>2026-07-19T18:52:59.563Z</t>
   </si>
   <si>
     <t>PBIO | Concessões de Recursos e Renúncias de Receitas</t>
@@ -484,7 +508,7 @@
     <t>acesso-a-informacao/auditorias/acoes-de-supervisao-controle-e-correicao</t>
   </si>
   <si>
-    <t>2026-07-19T11:39:03.154Z</t>
+    <t>2026-07-19T18:53:09.666Z</t>
   </si>
   <si>
     <t>PBIO | Supervisão, Controle e correição</t>
@@ -499,7 +523,7 @@
     <t>acesso-a-informacao/auditorias/demonstracoes-financeiras</t>
   </si>
   <si>
-    <t>2026-07-19T11:39:08.744Z</t>
+    <t>2026-07-19T18:53:14.710Z</t>
   </si>
   <si>
     <t>PBIO | Demonstrações Financeiras</t>
@@ -514,7 +538,7 @@
     <t>acesso-a-informacao/auditorias/prestacao-de-contas</t>
   </si>
   <si>
-    <t>2026-07-19T11:39:15.224Z</t>
+    <t>2026-07-19T18:53:20.468Z</t>
   </si>
   <si>
     <t>PBIO | Prestação de Contas</t>
@@ -529,7 +553,7 @@
     <t>acesso-a-informacao/auditorias/relatorios-da-cgu</t>
   </si>
   <si>
-    <t>2026-07-19T11:39:19.618Z</t>
+    <t>2026-07-19T18:53:27.672Z</t>
   </si>
   <si>
     <t>PBIO | Relatórios da CGU</t>
@@ -547,7 +571,7 @@
     <t>acesso-a-informacao/institucional/agenda-de-autoridades</t>
   </si>
   <si>
-    <t>2026-07-19T11:52:54.539Z</t>
+    <t>2026-07-19T18:52:02.133Z</t>
   </si>
   <si>
     <t>PBIO | Agenda de Autoridades</t>
@@ -562,7 +586,7 @@
     <t>acesso-a-informacao/institucional/atas</t>
   </si>
   <si>
-    <t>2026-07-19T11:38:01.888Z</t>
+    <t>2026-07-19T18:52:08.876Z</t>
   </si>
   <si>
     <t>PBIO | Atas</t>
@@ -577,7 +601,7 @@
     <t>acesso-a-informacao/institucional/atos-normativos</t>
   </si>
   <si>
-    <t>2026-07-19T11:38:07.463Z</t>
+    <t>2026-07-19T18:52:15.115Z</t>
   </si>
   <si>
     <t>PBIO | Atos normativos</t>
@@ -592,7 +616,7 @@
     <t>acesso-a-informacao/institucional/horario-de-atendimento</t>
   </si>
   <si>
-    <t>2026-07-19T11:38:11.770Z</t>
+    <t>2026-07-19T18:52:20.461Z</t>
   </si>
   <si>
     <t>PBIO | Horário de Atendimento</t>
@@ -607,7 +631,7 @@
     <t>acesso-a-informacao/institucional/hospitalidades</t>
   </si>
   <si>
-    <t>2026-07-19T11:38:16.176Z</t>
+    <t>2026-07-19T18:52:25.487Z</t>
   </si>
   <si>
     <t>PBIO | Hospitalidades Recebidas</t>
@@ -622,7 +646,7 @@
     <t>acesso-a-informacao/institucional/presentes</t>
   </si>
   <si>
-    <t>2026-07-19T11:38:23.020Z</t>
+    <t>2026-07-19T18:52:30.486Z</t>
   </si>
   <si>
     <t>PBIO | Presentes Recebidos</t>
@@ -637,7 +661,7 @@
     <t>acesso-a-informacao/institucional/sobre</t>
   </si>
   <si>
-    <t>2026-07-19T11:37:47.432Z</t>
+    <t>2026-07-19T18:51:53.157Z</t>
   </si>
   <si>
     <t>PBIO | Quem Somos</t>
@@ -652,7 +676,7 @@
     <t>acesso-a-informacao/licitacoes-e-contratos/aditivos</t>
   </si>
   <si>
-    <t>2026-07-19T11:39:54.935Z</t>
+    <t>2026-07-19T18:54:06.635Z</t>
   </si>
   <si>
     <t>PBIO | Aditivos</t>
@@ -667,7 +691,7 @@
     <t>acesso-a-informacao/licitacoes-e-contratos/contratos-de-transferencia-de-tecnologia</t>
   </si>
   <si>
-    <t>2026-07-19T11:40:09.000Z</t>
+    <t>2026-07-19T18:54:18.227Z</t>
   </si>
   <si>
     <t>PBIO | Contratos de Transferência de Tecnologia</t>
@@ -682,7 +706,7 @@
     <t>acesso-a-informacao/licitacoes-e-contratos/contratos</t>
   </si>
   <si>
-    <t>2026-07-19T11:40:02.294Z</t>
+    <t>2026-07-19T18:54:12.021Z</t>
   </si>
   <si>
     <t>PBIO | Contratos</t>
@@ -694,10 +718,13 @@
     <t>acesso-a-informacao/licitacoes-e-contratos/licitacoes.report.json</t>
   </si>
   <si>
+    <t>["hero-banner","embed","cards-content-panel-plain"]</t>
+  </si>
+  <si>
     <t>acesso-a-informacao/licitacoes-e-contratos/licitacoes</t>
   </si>
   <si>
-    <t>2026-07-19T11:40:17.478Z</t>
+    <t>2026-07-19T18:54:25.457Z</t>
   </si>
   <si>
     <t>PBIO | Licitações</t>
@@ -712,7 +739,7 @@
     <t>acesso-a-informacao/licitacoes-e-contratos/patrocinios</t>
   </si>
   <si>
-    <t>2026-07-19T11:40:22.984Z</t>
+    <t>2026-07-19T18:54:31.809Z</t>
   </si>
   <si>
     <t>PBIO | Patrocínios</t>
@@ -727,7 +754,7 @@
     <t>acesso-a-informacao/participacao-social/audiencias-publicas</t>
   </si>
   <si>
-    <t>2026-07-19T11:40:35.859Z</t>
+    <t>2026-07-19T18:54:42.720Z</t>
   </si>
   <si>
     <t>PBIO | Audiências Públicas</t>
@@ -742,7 +769,7 @@
     <t>acesso-a-informacao/participacao-social/conferencias</t>
   </si>
   <si>
-    <t>2026-07-19T11:40:40.486Z</t>
+    <t>2026-07-19T18:54:48.873Z</t>
   </si>
   <si>
     <t>PBIO | Conferências</t>
@@ -757,7 +784,7 @@
     <t>acesso-a-informacao/participacao-social/conselhos-e-orgaos-colegiados</t>
   </si>
   <si>
-    <t>2026-07-19T11:40:45.720Z</t>
+    <t>2026-07-19T18:54:53.756Z</t>
   </si>
   <si>
     <t>PBIO | Conselhos e Órgãos Colegiados</t>
@@ -772,7 +799,7 @@
     <t>acesso-a-informacao/participacao-social/editais-de-chamamento-publico</t>
   </si>
   <si>
-    <t>2026-07-19T11:40:50.831Z</t>
+    <t>2026-07-19T18:54:59.430Z</t>
   </si>
   <si>
     <t>PBIO | Editais de Chamamento Público</t>
@@ -787,7 +814,7 @@
     <t>acesso-a-informacao/participacao-social/outras-acoes</t>
   </si>
   <si>
-    <t>2026-07-19T11:40:55.397Z</t>
+    <t>2026-07-19T18:55:04.294Z</t>
   </si>
   <si>
     <t>PBIO | Outras Ações</t>
@@ -802,7 +829,7 @@
     <t>acesso-a-informacao/participacao-social/ouvidoria</t>
   </si>
   <si>
-    <t>2026-07-19T11:41:01.714Z</t>
+    <t>2026-07-19T19:04:45.628Z</t>
   </si>
   <si>
     <t>PBIO | Ouvidoria</t>
@@ -817,7 +844,7 @@
     <t>acesso-a-informacao/receitas-e-despesas/alienacao-de-bens-imoveis</t>
   </si>
   <si>
-    <t>2026-07-19T11:41:20.846Z</t>
+    <t>2026-07-19T19:05:02.648Z</t>
   </si>
   <si>
     <t>PBIO | Alienação de Bens Imóveis</t>
@@ -832,7 +859,7 @@
     <t>acesso-a-informacao/receitas-e-despesas/aquisicao-de-bens</t>
   </si>
   <si>
-    <t>2026-07-19T11:41:27.311Z</t>
+    <t>2026-07-19T19:05:10.605Z</t>
   </si>
   <si>
     <t>PBIO | Aquisição de Bens</t>
@@ -847,7 +874,7 @@
     <t>acesso-a-informacao/receitas-e-despesas/diarias-e-passagens</t>
   </si>
   <si>
-    <t>2026-07-19T11:41:32.931Z</t>
+    <t>2026-07-19T19:05:16.385Z</t>
   </si>
   <si>
     <t>PBIO | Diárias e Passagens</t>
@@ -865,7 +892,7 @@
     <t>acesso-a-informacao/receitas-e-despesas/orcamento-de-investimento</t>
   </si>
   <si>
-    <t>2026-07-19T11:41:39.094Z</t>
+    <t>2026-07-19T19:05:21.948Z</t>
   </si>
   <si>
     <t>PBIO | Orçamento de Investimento</t>
@@ -880,7 +907,7 @@
     <t>acesso-a-informacao/receitas-e-despesas/politica-de-dividendos</t>
   </si>
   <si>
-    <t>2026-07-19T11:41:45.080Z</t>
+    <t>2026-07-19T19:05:27.115Z</t>
   </si>
   <si>
     <t>PBIO | Política de Dividendos</t>
@@ -895,7 +922,7 @@
     <t>acesso-a-informacao/receitas-e-despesas/politica-de-transacoes-com-partes-relacionadas</t>
   </si>
   <si>
-    <t>2026-07-19T11:41:50.583Z</t>
+    <t>2026-07-19T19:05:32.944Z</t>
   </si>
   <si>
     <t>PBIO | Política de Transações</t>
@@ -910,7 +937,7 @@
     <t>acesso-a-informacao/receitas-e-despesas/publicidade</t>
   </si>
   <si>
-    <t>2026-07-19T11:41:56.011Z</t>
+    <t>2026-07-19T19:05:38.268Z</t>
   </si>
   <si>
     <t>PBIO | Publicidade</t>
@@ -925,7 +952,7 @@
     <t>acesso-a-informacao/receitas-e-despesas/receitas</t>
   </si>
   <si>
-    <t>2026-07-19T11:42:01.484Z</t>
+    <t>2026-07-19T19:05:44.597Z</t>
   </si>
   <si>
     <t>PBIO | Receitas</t>
@@ -940,7 +967,7 @@
     <t>acesso-a-informacao/servico-de-informacao-ao-cidadao-sic/balcoes-de-atendimento</t>
   </si>
   <si>
-    <t>2026-07-19T11:42:20.110Z</t>
+    <t>2026-07-19T19:06:01.870Z</t>
   </si>
   <si>
     <t>PBIO | Atendimento</t>
@@ -955,7 +982,7 @@
     <t>acesso-a-informacao/servico-de-informacao-ao-cidadao-sic/estatisticas-do-sic</t>
   </si>
   <si>
-    <t>2026-07-19T11:42:24.836Z</t>
+    <t>2026-07-19T19:06:08.634Z</t>
   </si>
   <si>
     <t>PBIO | Estatísticas do SIC</t>
@@ -1425,131 +1452,131 @@
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" t="s">
         <v>34</v>
       </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" t="s">
-        <v>32</v>
-      </c>
       <c r="H6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -1558,24 +1585,24 @@
         <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G8" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="H8" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s">
         <v>48</v>
       </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
@@ -1584,24 +1611,24 @@
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G9" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="H9" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
@@ -1610,24 +1637,24 @@
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G10" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H10" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -1636,24 +1663,24 @@
         <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G11" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H11" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
@@ -1662,24 +1689,24 @@
         <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H12" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
@@ -1688,24 +1715,24 @@
         <v>12</v>
       </c>
       <c r="F13" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G13" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H13" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
@@ -1714,24 +1741,24 @@
         <v>12</v>
       </c>
       <c r="F14" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G14" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H14" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
@@ -1740,24 +1767,24 @@
         <v>12</v>
       </c>
       <c r="F15" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G15" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
@@ -1766,24 +1793,24 @@
         <v>12</v>
       </c>
       <c r="F16" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G16" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H16" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
@@ -1792,24 +1819,24 @@
         <v>12</v>
       </c>
       <c r="F17" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H17" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
@@ -1818,24 +1845,24 @@
         <v>12</v>
       </c>
       <c r="F18" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G18" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="H18" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
@@ -1844,24 +1871,24 @@
         <v>12</v>
       </c>
       <c r="F19" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G19" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="H19" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
@@ -1870,24 +1897,24 @@
         <v>12</v>
       </c>
       <c r="F20" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G20" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H20" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
@@ -1896,128 +1923,128 @@
         <v>12</v>
       </c>
       <c r="F21" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G21" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H21" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
       </c>
       <c r="E22" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G22" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H22" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B23" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F23" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G23" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="H23" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B24" t="s">
-        <v>17</v>
+        <v>131</v>
       </c>
       <c r="C24" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G24" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="H24" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
+        <v>137</v>
       </c>
       <c r="C25" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="G25" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="H25" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="B26" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="C26" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
@@ -2026,24 +2053,24 @@
         <v>12</v>
       </c>
       <c r="F26" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G26" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H26" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B27" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="C27" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
@@ -2052,24 +2079,24 @@
         <v>12</v>
       </c>
       <c r="F27" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="G27" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="H27" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B28" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
@@ -2078,24 +2105,24 @@
         <v>12</v>
       </c>
       <c r="F28" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="G28" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="H28" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B29" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="C29" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
@@ -2104,24 +2131,24 @@
         <v>12</v>
       </c>
       <c r="F29" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="G29" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H29" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B30" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
@@ -2130,24 +2157,24 @@
         <v>12</v>
       </c>
       <c r="F30" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="G30" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H30" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B31" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
@@ -2156,24 +2183,24 @@
         <v>12</v>
       </c>
       <c r="F31" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="G31" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="H31" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B32" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C32" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D32" t="s">
         <v>11</v>
@@ -2182,24 +2209,24 @@
         <v>12</v>
       </c>
       <c r="F32" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="G32" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="H32" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B33" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C33" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D33" t="s">
         <v>11</v>
@@ -2208,24 +2235,24 @@
         <v>12</v>
       </c>
       <c r="F33" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="G33" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H33" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B34" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C34" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="D34" t="s">
         <v>11</v>
@@ -2234,24 +2261,24 @@
         <v>12</v>
       </c>
       <c r="F34" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="G34" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="H34" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="C35" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D35" t="s">
         <v>11</v>
@@ -2260,24 +2287,24 @@
         <v>12</v>
       </c>
       <c r="F35" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="G35" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H35" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B36" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C36" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="D36" t="s">
         <v>11</v>
@@ -2286,24 +2313,24 @@
         <v>12</v>
       </c>
       <c r="F36" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="G36" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="H36" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B37" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C37" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="D37" t="s">
         <v>11</v>
@@ -2312,24 +2339,24 @@
         <v>12</v>
       </c>
       <c r="F37" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="G37" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="H37" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B38" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="C38" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="D38" t="s">
         <v>11</v>
@@ -2338,24 +2365,24 @@
         <v>12</v>
       </c>
       <c r="F38" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="G38" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H38" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="C39" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D39" t="s">
         <v>11</v>
@@ -2364,24 +2391,24 @@
         <v>12</v>
       </c>
       <c r="F39" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="G39" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="H39" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B40" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C40" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="D40" t="s">
         <v>11</v>
@@ -2390,24 +2417,24 @@
         <v>12</v>
       </c>
       <c r="F40" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="G40" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="H40" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B41" t="s">
-        <v>17</v>
+        <v>184</v>
       </c>
       <c r="C41" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="D41" t="s">
         <v>11</v>
@@ -2416,24 +2443,24 @@
         <v>12</v>
       </c>
       <c r="F41" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="G41" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="H41" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B42" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="C42" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="D42" t="s">
         <v>11</v>
@@ -2442,24 +2469,24 @@
         <v>12</v>
       </c>
       <c r="F42" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="G42" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="H42" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B43" t="s">
-        <v>17</v>
+        <v>184</v>
       </c>
       <c r="C43" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="D43" t="s">
         <v>11</v>
@@ -2468,24 +2495,24 @@
         <v>12</v>
       </c>
       <c r="F43" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="G43" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="H43" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>235</v>
       </c>
       <c r="C44" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="D44" t="s">
         <v>11</v>
@@ -2494,24 +2521,24 @@
         <v>12</v>
       </c>
       <c r="F44" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="G44" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="H44" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="B45" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="C45" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="D45" t="s">
         <v>11</v>
@@ -2520,24 +2547,24 @@
         <v>12</v>
       </c>
       <c r="F45" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G45" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="H45" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="B46" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="C46" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="D46" t="s">
         <v>11</v>
@@ -2546,24 +2573,24 @@
         <v>12</v>
       </c>
       <c r="F46" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="G46" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H46" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="B47" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C47" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="D47" t="s">
         <v>11</v>
@@ -2572,24 +2599,24 @@
         <v>12</v>
       </c>
       <c r="F47" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="G47" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="H47" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B48" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C48" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="D48" t="s">
         <v>11</v>
@@ -2598,24 +2625,24 @@
         <v>12</v>
       </c>
       <c r="F48" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="G48" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="H48" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="B49" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C49" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="D49" t="s">
         <v>11</v>
@@ -2624,24 +2651,24 @@
         <v>12</v>
       </c>
       <c r="F49" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="G49" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="H49" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="C50" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="D50" t="s">
         <v>11</v>
@@ -2650,24 +2677,24 @@
         <v>12</v>
       </c>
       <c r="F50" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="G50" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="H50" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="B51" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C51" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="D51" t="s">
         <v>11</v>
@@ -2676,24 +2703,24 @@
         <v>12</v>
       </c>
       <c r="F51" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="G51" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="H51" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="B52" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C52" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="D52" t="s">
         <v>11</v>
@@ -2702,24 +2729,24 @@
         <v>12</v>
       </c>
       <c r="F52" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="G52" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="H52" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="B53" t="s">
-        <v>17</v>
+        <v>184</v>
       </c>
       <c r="C53" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="D53" t="s">
         <v>11</v>
@@ -2728,24 +2755,24 @@
         <v>12</v>
       </c>
       <c r="F53" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="G53" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="H53" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="C54" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="D54" t="s">
         <v>11</v>
@@ -2754,24 +2781,24 @@
         <v>12</v>
       </c>
       <c r="F54" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="G54" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="H54" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="B55" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="C55" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="D55" t="s">
         <v>11</v>
@@ -2780,24 +2807,24 @@
         <v>12</v>
       </c>
       <c r="F55" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="G55" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="H55" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B56" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C56" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="D56" t="s">
         <v>11</v>
@@ -2806,24 +2833,24 @@
         <v>12</v>
       </c>
       <c r="F56" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="G56" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="H56" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="B57" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C57" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="D57" t="s">
         <v>11</v>
@@ -2832,24 +2859,24 @@
         <v>12</v>
       </c>
       <c r="F57" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="G57" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="H57" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="B58" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="C58" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="D58" t="s">
         <v>11</v>
@@ -2858,24 +2885,24 @@
         <v>12</v>
       </c>
       <c r="F58" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="G58" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="H58" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="B59" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C59" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="D59" t="s">
         <v>11</v>
@@ -2884,24 +2911,24 @@
         <v>12</v>
       </c>
       <c r="F59" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="G59" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="H59" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="B60" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C60" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="D60" t="s">
         <v>11</v>
@@ -2910,24 +2937,24 @@
         <v>12</v>
       </c>
       <c r="F60" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="G60" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="H60" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="B61" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C61" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="D61" t="s">
         <v>11</v>
@@ -2936,13 +2963,13 @@
         <v>12</v>
       </c>
       <c r="F61" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="G61" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="H61" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
